--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA168"/>
+  <dimension ref="A1:AA171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18173,6 +18173,345 @@
       <c r="Z168" s="2" t="inlineStr"/>
       <c r="AA168" s="2" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ignaciogonzaleznieto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Angela Farfán Gonzales</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Head of Business Development</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angela-farf%C3%A1n-gonzales-633b12239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>Ismael Gianfranco Grijalva Paiva</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sommelier </t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ismael-gianfranco-grijalva-paiva-924105191/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA171"/>
+  <dimension ref="A1:AA174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18512,6 +18512,345 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ignaciogonzaleznieto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>Angela Farfán Gonzales</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>Head of Business Development</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angela-farf%C3%A1n-gonzales-633b12239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Ismael Gianfranco Grijalva Paiva</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sommelier </t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ismael-gianfranco-grijalva-paiva-924105191/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA174"/>
+  <dimension ref="A1:AA179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18851,6 +18851,527 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Wong Larco</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Wong Larco</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>85817</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Trujillo</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>857 Avenida Larco</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>13008</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wong.pe</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>wongoficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 6138888</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr"/>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WongOficial</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wongperu/</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/WongPeru</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr"/>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Despensa De La Selva S.a.c.</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Despensa De La Selva S.a.c.</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>121791</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Chiclayo</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Lambayeque</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>1195 Avenida Salaverry</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>14009</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.despensadelaselva.com</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>hola@despensadelaselva.com</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>20603215088</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/despensa.selva</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr"/>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ignaciogonzaleznieto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>Angela Farfán Gonzales</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>Head of Business Development</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angela-farf%C3%A1n-gonzales-633b12239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>Ismael Gianfranco Grijalva Paiva</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sommelier </t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ismael-gianfranco-grijalva-paiva-924105191/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA179"/>
+  <dimension ref="A1:AA185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19372,6 +19372,628 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Hiper Plazavea Chiclayo</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Hiper Plazavea Chiclayo</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>85476</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Ventanilla</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Callao, Callao</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>5002 Avenida Nestor Gambetta</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>07056</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.plazavea.com.pe</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@spsa.pe</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 6258000</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plazavea-hiper/</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazaVeaOficial/</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazavea.oficial/</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/plazavea</t>
+        </is>
+      </c>
+      <c r="V180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/PlazaVeaOficial/</t>
+        </is>
+      </c>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr"/>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Wong Larco</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Wong Larco</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>85817</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Trujillo</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>857 Avenida Larco</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>13008</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wong.pe</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>wongoficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 6138888</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WongOficial</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wongperu/</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/WongPeru</t>
+        </is>
+      </c>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr"/>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Despensa De La Selva S.a.c.</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Despensa De La Selva S.a.c.</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>121791</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Chiclayo</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Lambayeque</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1195 Avenida Salaverry</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>14009</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.despensadelaselva.com</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>hola@despensadelaselva.com</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr"/>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>20603215088</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/despensa.selva</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr"/>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ignaciogonzaleznieto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>Angela Farfán Gonzales</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>Head of Business Development</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angela-farf%C3%A1n-gonzales-633b12239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Gastronia Sac</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>472 Calle Bolívar</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>ventas@gastronia.com.pe</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 2748988</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>20550207525</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gastronia-sac/</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GastroniaSAC</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gastroniaperu</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>Ismael Gianfranco Grijalva Paiva</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sommelier </t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ismael-gianfranco-grijalva-paiva-924105191/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA185"/>
+  <dimension ref="A1:AA186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19994,6 +19994,95 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Inversiones Liqueur Beef E.i.r.l.</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Inversiones Liqueur Beef E.i.r.l.</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>121802</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>993 Avenida San Luis</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>15021</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://liqueurbeef.com</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>ventas@liqueurbeef.com</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>20606617969</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Liqueurbeef/</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/liqueurbeef</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr"/>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA186"/>
+  <dimension ref="A1:AA187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20083,6 +20083,95 @@
       <c r="Z186" s="2" t="inlineStr"/>
       <c r="AA186" s="2" t="inlineStr"/>
     </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Inversiones Liqueur Beef E.i.r.l.</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Inversiones Liqueur Beef E.i.r.l.</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>121802</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>993 Avenida San Luis</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>15021</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://liqueurbeef.com</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>ventas@liqueurbeef.com</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr"/>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>20606617969</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Liqueurbeef/</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/liqueurbeef</t>
+        </is>
+      </c>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr"/>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA187"/>
+  <dimension ref="A1:AA188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20172,6 +20172,83 @@
       <c r="Z187" s="2" t="inlineStr"/>
       <c r="AA187" s="2" t="inlineStr"/>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Vintragos Licorería</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Vintragos Licorería</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>85319</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Víctor Larco Herrera</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>La Libertad, Trujillo</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>30 Avenida Prolongación César Vallejo</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>13008</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vintragos.com</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>vintragosadm@gmail.com</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr"/>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr"/>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vintragos/</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vintragoslicoreria/</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr"/>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA188"/>
+  <dimension ref="A1:AA189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20249,6 +20249,71 @@
       <c r="Z188" s="2" t="inlineStr"/>
       <c r="AA188" s="2" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>L'ESPRIT DU VIN</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>168178</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Calle Berlín 644</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://lespritduvinperu.com</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>ventas@lespritduvinperu.com</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr"/>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr"/>
+      <c r="R189" s="2" t="inlineStr"/>
+      <c r="S189" s="2" t="inlineStr"/>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lespritduvinperu_vinos/</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr"/>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA189"/>
+  <dimension ref="A1:AA191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20314,6 +20314,200 @@
       <c r="Z189" s="2" t="inlineStr"/>
       <c r="AA189" s="2" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr">
+        <is>
+          <t>Manuel A.</t>
+        </is>
+      </c>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-a-zavaleta-haro-4760a74a/?originalSubdomain=pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr"/>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>Cristhian Torres</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristhiantorres/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA191"/>
+  <dimension ref="A1:AA193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20508,6 +20508,200 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>Manuel A.</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-a-zavaleta-haro-4760a74a/?originalSubdomain=pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr"/>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>Cristhian Torres</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristhiantorres/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA193"/>
+  <dimension ref="A1:AA195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20702,6 +20702,200 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>Manuel A.</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-a-zavaleta-haro-4760a74a/?originalSubdomain=pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr"/>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>Cristhian Torres</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristhiantorres/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA195"/>
+  <dimension ref="A1:AA197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20896,6 +20896,200 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr">
+        <is>
+          <t>Manuel A.</t>
+        </is>
+      </c>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-a-zavaleta-haro-4760a74a/?originalSubdomain=pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr"/>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>Cristhian Torres</t>
+        </is>
+      </c>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristhiantorres/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA197"/>
+  <dimension ref="A1:AA199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21090,6 +21090,200 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Manuel A.</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-a-zavaleta-haro-4760a74a/?originalSubdomain=pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Licorerias Unidas</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Santiago de Surco</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>493 Avenida Club Golf los Incas</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>info@licoreriasunidas.pe</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>+51 1 4800424</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr"/>
+      <c r="Q199" s="2" t="inlineStr"/>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/licorer%C3%ADas-unidas/</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoreriasunidas.peru</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/licoreriasunidas/</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr">
+        <is>
+          <t>Cristhian Torres</t>
+        </is>
+      </c>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristhiantorres/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
